--- a/hasil_ranking_fuzzy.xlsx
+++ b/hasil_ranking_fuzzy.xlsx
@@ -448,85 +448,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Citra</t>
+          <t>Kurnia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.9000000000000004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kurnia</t>
+          <t>Putri</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.2800000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Putri</t>
+          <t>Citra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.2666666666666666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hani</t>
+          <t>Andi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andi</t>
+          <t>Dedi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nana</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03125000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dedi</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -539,7 +539,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Eka</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -552,7 +552,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Hani</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -578,7 +578,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fajar</t>
+          <t>Joko</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -591,7 +591,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eka</t>
+          <t>Fajar</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -617,7 +617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joko</t>
+          <t>Miko</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -630,7 +630,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miko</t>
+          <t>Nana</t>
         </is>
       </c>
       <c r="B16" t="n">
